--- a/12629126.xlsx
+++ b/12629126.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditi mandal\Documents\lpu 1st sem\Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6B8B59-3A93-4454-83D0-6DA99B62AEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,6 +197,18 @@
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
+    <t>Aditi Mandal</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>MCA (D2634)</t>
+  </si>
+  <si>
+    <t>Hello</t>
   </si>
 </sst>
 </file>
@@ -852,8 +862,10 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -885,26 +897,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>54</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12629126</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1016,7 +1036,9 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
+      <c r="A7" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>

--- a/12629126.xlsx
+++ b/12629126.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditi mandal\Documents\lpu 1st sem\Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6B8B59-3A93-4454-83D0-6DA99B62AEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D540EA4D-DD32-4356-A1A5-BE74D6516273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,7 +208,37 @@
     <t>MCA (D2634)</t>
   </si>
   <si>
-    <t>Hello</t>
+    <t>enlightened</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>peaceful</t>
+  </si>
+  <si>
+    <t>delighted</t>
+  </si>
+  <si>
+    <t>okayish</t>
+  </si>
+  <si>
+    <t>nice</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>felt peaceful with my own thoughts</t>
+  </si>
+  <si>
+    <t>had a grat movie night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">took on a new habbit </t>
+  </si>
+  <si>
+    <t>bit stressfull because of multiple CA</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1021,7 @@
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46223</v>
+        <v>46279</v>
       </c>
       <c r="B6" s="9">
         <v>420</v>
@@ -1035,98 +1065,194 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B7" s="14">
+        <v>360</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14">
+        <v>250</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>20</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="1"/>
+        <v>580</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16">
+        <v>10</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B8" s="14">
+        <v>370</v>
+      </c>
+      <c r="C8" s="14">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14">
+        <v>200</v>
+      </c>
+      <c r="E8" s="14">
+        <v>45</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>25</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+        <v>405</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="16">
+        <v>10</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B9" s="14">
+        <v>350</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>45</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+        <v>505</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="16">
+        <v>10</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B10" s="14">
+        <v>370</v>
+      </c>
+      <c r="C10" s="14">
+        <v>20</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>20</v>
+      </c>
+      <c r="F10" s="14">
+        <v>350</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>20</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="16">
+        <v>6</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
+      <c r="A11" s="8">
+        <v>46284</v>
+      </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -1148,7 +1274,9 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="8">
+        <v>46285</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1170,7 +1298,9 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
+      <c r="A13" s="8">
+        <v>46286</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1192,7 +1322,9 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="8">
+        <v>46287</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1214,7 +1346,9 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="8">
+        <v>46288</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1236,7 +1370,9 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="8">
+        <v>46289</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1258,7 +1394,9 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="8">
+        <v>46290</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1280,7 +1418,9 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="8">
+        <v>46291</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>

--- a/12629126.xlsx
+++ b/12629126.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditi mandal\Documents\lpu 1st sem\Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D540EA4D-DD32-4356-A1A5-BE74D6516273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB2D480-46B1-4969-9C4F-7DFB46AAC18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>bit stressfull because of multiple CA</t>
+  </si>
+  <si>
+    <t>bit off</t>
+  </si>
+  <si>
+    <t>happen to sleep early after classes</t>
+  </si>
+  <si>
+    <t>coding with music on</t>
   </si>
 </sst>
 </file>
@@ -1249,53 +1258,97 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>46284</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="B11" s="14">
+        <v>380</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>45</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14">
+        <v>20</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="16">
+        <v>5</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>46285</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>500</v>
+      </c>
+      <c r="C12" s="14">
+        <v>15</v>
+      </c>
+      <c r="D12" s="14">
+        <v>200</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>80</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16">
+        <v>8</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
